--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gentiva</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,172 +496,172 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4979b99382efe90b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
+          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>A L P</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Database Architect-Transportation Data Collection-Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Quality Counts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,137 +671,137 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
@@ -893,55 +893,55 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,495 +951,75 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AssistRx</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Maitland, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Grainger</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Governance Senior</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AST SpaceMobile</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Lanham, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ascension</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Driven Brands</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Teradata Developer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c3b32f6f53279a94</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,87 +538,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>A L P</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Database Architect-Transportation Data Collection-Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A L P</t>
+          <t>Quality Counts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
+          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Database Architect-Transportation Data Collection-Remote</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quality Counts</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,38 +832,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -880,146 +880,6 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Driven Brands</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c3b32f6f53279a94</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -538,12 +538,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A L P</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,73 +552,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc1e10f9afcac16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Database Architect-Transportation Data Collection-Remote</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quality Counts</t>
+          <t>A L P</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
+          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Database Architect-Transportation Data Collection-Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Quality Counts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
+          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>A L P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Architect-Transportation Data Collection-Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quality Counts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc1e10f9afcac16</t>
+          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A L P</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Database Architect-Transportation Data Collection-Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quality Counts</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,2002 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Honolulu, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Engineer -.NET</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>10.4</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b32f6f53279a94</t>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Architect-Transportation Data Collection-Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quality Counts</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2770,76 +2770,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Engineer -.NET</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,50 +2726,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,15 +2726,50 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,12 +503,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A L P</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,108 +517,108 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc1e10f9afcac16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>A L P</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,15 +2761,50 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,50 +2761,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc1e10f9afcac16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>A L P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc1e10f9afcac16</t>
+          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A L P</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,50 +2726,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Database Architect-Transportation Data Collection-Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Quality Counts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
+          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,87 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3b32f6f53279a94</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Architect-Transportation Data Collection-Remote</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quality Counts</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,87 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b32f6f53279a94</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-22.xlsx
+++ b/results/job_matches_2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - West</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc1e10f9afcac16</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf94c93449dfa3d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - Central</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A L P</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,124 +531,124 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
+          <t>https://www.indeed.com/viewjob?jk=23fa7ab7f29d61af</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Architect-Transportation Data Collection-Remote</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quality Counts</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a65847d8f6c718</t>
+          <t>https://www.indeed.com/viewjob?jk=ff8fbb8c2cb45e2e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc1e10f9afcac16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>A L P</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,52 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b32f6f53279a94</t>
+          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cee995a368e6f967</t>
         </is>
       </c>
     </row>
